--- a/Q2. Logical Functions.xlsx
+++ b/Q2. Logical Functions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\ExcleR\Excel Assignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA2F353-0EDA-43D1-97A6-52FD3796221F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8906C6AF-B554-406E-84FE-A140C4A10C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -868,7 +868,7 @@
         <v>RETIRED</v>
       </c>
       <c r="M10" s="11" t="str">
-        <f>IF(AND(OR(G10="Sales",G10="Marketing",G10="Inside Sales",G10="Digital Marketing"),H10&lt;45000),"GET BONUS 25000","NO BONUS")</f>
+        <f>IF(AND(OR(G10="Sales",G10="Marketing"),H10&lt;45000),"GET BONUS 25000","NO BONUS")</f>
         <v>NO BONUS</v>
       </c>
       <c r="N10" s="11" t="str">
@@ -917,7 +917,7 @@
         <v>RETIRED</v>
       </c>
       <c r="M11" s="11" t="str">
-        <f t="shared" ref="M11:M47" si="3">IF(AND(OR(G11="Sales",G11="Marketing",G11="Inside Sales",G11="Digital Marketing"),H11&lt;45000),"GET BONUS 25000","NO BONUS")</f>
+        <f t="shared" ref="M11:M47" si="3">IF(AND(OR(G11="Sales",G11="Marketing"),H11&lt;45000),"GET BONUS 25000","NO BONUS")</f>
         <v>GET BONUS 25000</v>
       </c>
       <c r="N11" s="11" t="str">
@@ -967,7 +967,7 @@
       </c>
       <c r="M12" s="11" t="str">
         <f t="shared" si="3"/>
-        <v>GET BONUS 25000</v>
+        <v>NO BONUS</v>
       </c>
       <c r="N12" s="11" t="str">
         <f t="shared" si="4"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="M20" s="11" t="str">
         <f t="shared" si="3"/>
-        <v>GET BONUS 25000</v>
+        <v>NO BONUS</v>
       </c>
       <c r="N20" s="11" t="str">
         <f t="shared" si="4"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="M47" s="11" t="str">
         <f t="shared" si="3"/>
-        <v>GET BONUS 25000</v>
+        <v>NO BONUS</v>
       </c>
       <c r="N47" s="11" t="str">
         <f t="shared" si="4"/>
@@ -3653,22 +3653,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10:K47">
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="9000 bonous">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="9000 bonous">
       <formula>NOT(ISERROR(SEARCH("9000 bonous",K10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10:L47">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="RETIRED">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="RETIRED">
       <formula>NOT(ISERROR(SEARCH("RETIRED",L10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:M47">
-    <cfRule type="notContainsText" dxfId="2" priority="2" operator="notContains" text="NO BONOUS">
+    <cfRule type="notContainsText" dxfId="1" priority="2" operator="notContains" text="NO BONOUS">
       <formula>ISERROR(SEARCH("NO BONOUS",M10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:N47">
-    <cfRule type="notContainsText" dxfId="1" priority="1" operator="notContains" text="NO GIFT">
+    <cfRule type="notContainsText" dxfId="0" priority="1" operator="notContains" text="NO GIFT">
       <formula>ISERROR(SEARCH("NO GIFT",N10))</formula>
     </cfRule>
   </conditionalFormatting>
